--- a/debug/excel_overviews/gpt-4.1_vs_Llama-2-7b-chat-hf/Llama-3.1-8B-Instruct/default/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Llama-2-7b-chat-hf/Llama-3.1-8B-Instruct/default/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>10</v>
+        <v>172</v>
       </c>
       <c r="D2">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>52</v>
       </c>
       <c r="G2">
-        <v>406</v>
+        <v>170</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>8</v>
+        <v>212</v>
       </c>
       <c r="D3">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="G3">
-        <v>404</v>
+        <v>159</v>
       </c>
       <c r="H3">
         <v>426</v>

--- a/debug/excel_overviews/gpt-4.1_vs_Llama-2-7b-chat-hf/Llama-3.1-8B-Instruct/default/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Llama-2-7b-chat-hf/Llama-3.1-8B-Instruct/default/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>172</v>
+        <v>127</v>
       </c>
       <c r="D2">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="E2">
         <v>52</v>
       </c>
       <c r="G2">
-        <v>170</v>
+        <v>227</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>212</v>
+        <v>175</v>
       </c>
       <c r="D3">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E3">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="G3">
-        <v>159</v>
+        <v>208</v>
       </c>
       <c r="H3">
         <v>426</v>
